--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CreditRightsManagement001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CreditRightsManagement001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14660" windowHeight="3350"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
@@ -26,11 +25,10 @@
     <t>生效日</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>风险权数%</t>
   </si>
   <si>
-    <t>风险权数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -85,15 +83,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -135,7 +130,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -170,7 +165,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -380,16 +375,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.36328125" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.90625" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -400,10 +395,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
